--- a/Design/Excel/GameHot/Datas/Buqi/BuqiItem.xlsx
+++ b/Design/Excel/GameHot/Datas/Buqi/BuqiItem.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>加急通知</t>
+          <t>急攻令</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -597,12 +597,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>fast|haste</t>
+          <t>attack|haste</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OnUse,Damage,EnemyExecution,4,30,W8-003-damage,None,0,0,0,0,false,true|OnUse,Haste,LeftAdjacentItem,2000,30,W8-003-haste,None,0,0,0,0,false,true</t>
+          <t>OnUse,Damage,EnemyExecution,4,30,W8-003-attack,None,0,0,0,0,false,true|OnUse,Haste,LeftAdjacentItem,2000,30,W8-003-haste,None,0,0,0,0,false,true</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>冲刺看板</t>
+          <t>冲锋看板</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>fast|charge</t>
+          <t>attack|charge</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OnAdjacentUse,Charge,Self,1,30,W8-005-adjacent-charge,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,6,30,W8-005-damage,None,0,0,3,2,true,true</t>
+          <t>OnAdjacentUse,Charge,Self,1,30,W8-005-adjacent-charge,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,6,30,W8-005-attack,None,0,0,3,2,true,true</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>截止日</t>
+          <t>终局重锤</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>fast|core|noise</t>
+          <t>attack|core|overload</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OnBattleStart,Haste,AllAdjacentItems,1500,50,W8-006-opening-haste,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,16,30,W8-006-damage,None,0,0,0,0,false,true|OnUse,Noise,Self,2,30,W8-006-noise,None,0,0,0,0,false,true</t>
+          <t>OnBattleStart,Haste,AllAdjacentItems,1500,50,W8-006-opening-haste,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,16,30,W8-006-attack,None,0,0,0,0,false,true|OnUse,Noise,Self,2,30,W8-006-overload,None,0,0,0,0,false,true</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>临时缓冲</t>
+          <t>小护盾</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>buffer</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OnUse,Buffer,Self,7,30,W8-007-buffer,None,0,0,0,0,false,true</t>
+          <t>OnUse,Buffer,Self,7,30,W8-007-shield,None,0,0,0,0,false,true</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>风险清单</t>
+          <t>破盾清单</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>buffer|charge</t>
+          <t>shield|charge</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OnUse,Charge,Self,1,30,W8-008-charge,None,0,0,0,0,false,true|OnFirstConditionMet,Damage,EnemyExecution,8,30,W8-008-buffer-counter,BufferLost,0,0,0,0,false,true</t>
+          <t>OnUse,Charge,Self,1,30,W8-008-charge,None,0,0,0,0,false,true|OnFirstConditionMet,Damage,EnemyExecution,8,30,W8-008-shield-break,BufferLost,0,0,0,0,false,true</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>灾备中心</t>
+          <t>堡垒核心</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>buffer|core</t>
+          <t>shield|core</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OnUse,Buffer,Self,12,30,W8-012-buffer,None,0,0,0,0,false,true|OnFirstConditionMet,Damage,EnemyExecution,14,30,W8-012-buffer-counter,BufferLost,0,0,0,0,false,true</t>
+          <t>OnUse,Buffer,Self,12,30,W8-012-shield,None,0,0,0,0,false,true|OnFirstConditionMet,Damage,EnemyExecution,14,30,W8-012-shield-break,BufferLost,0,0,0,0,false,true</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>交接单</t>
+          <t>传能接线</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OnUse,Damage,EnemyExecution,4,30,W8-013-damage,None,0,0,0,0,false,true|OnUse,Charge,RightAdjacentItem,1,30,W8-013-pass-charge,None,0,0,0,0,false,true|OnAdjacentUse,Charge,RightAdjacentItem,1,30,W8-013-adjacent-pass,None,0,0,0,0,false,true</t>
+          <t>OnUse,Damage,EnemyExecution,4,30,W8-013-attack,None,0,0,0,0,false,true|OnUse,Charge,RightAdjacentItem,1,30,W8-013-pass-charge,None,0,0,0,0,false,true|OnAdjacentUse,Charge,RightAdjacentItem,1,30,W8-013-adjacent-pass,None,0,0,0,0,false,true</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>联签流程</t>
+          <t>连击印</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OnAdjacentUse,Charge,Self,1,30,W8-014-adjacent-charge,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,3,30,W8-014-damage,None,0,0,2,3,true,true</t>
+          <t>OnAdjacentUse,Charge,Self,1,30,W8-014-adjacent-charge,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,3,30,W8-014-attack,None,0,0,2,3,true,true</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>流程节点</t>
+          <t>节奏节点</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -906,7 +906,577 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OnAdjacentUse,Haste,Self,2000,30,W8-015-adjacent-haste,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,7,30,W8-015-damage,None,0,0,0,0,false,true</t>
+          <t>OnAdjacentUse,Haste,Self,2000,30,W8-015-adjacent-haste,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,7,30,W8-015-attack,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>W8-016</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>急救包</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>45</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OnUse,Heal,Self,8,30,W8-016-heal,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>W8-017</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>回春泉</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>70</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>heal|regen|shield</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OnUse,Regen,Self,4,50,W8-017-regen,None,0,0,0,0,false,true|OnUse,Buffer,Self,5,30,W8-017-shield,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>W8-018</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>救援旗</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>95</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>heal|regen|core|haste</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>OnBattleStart,Regen,Self,3,60,W8-018-opening-regen,None,0,0,0,0,false,true|OnUse,Heal,Self,15,30,W8-018-heal,None,0,0,0,0,false,true|OnUse,Haste,AllAdjacentItems,1200,30,W8-018-haste,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>W8-019</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>毒针</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>OnUse,Poison,EnemyExecution,3,40,W8-019-poison,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>W8-020</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>腐蚀瓶</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>65</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>poison|slow</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>OnUse,Poison,EnemyExecution,5,50,W8-020-poison,None,0,0,0,0,false,true|OnUse,Delay,ShortestCooldownEnemyItem,1000,30,W8-020-slow,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>W8-021</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>毒雾炉</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>90</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>poison|core|overload</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>OnUse,Poison,EnemyExecution,7,60,W8-021-poison,None,0,0,0,0,false,true|OnUse,Noise,Self,1,30,W8-021-overload,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>W8-022</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>火花符</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>38</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OnUse,Burn,EnemyExecution,3,30,W8-022-burn,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>W8-023</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>炽焰炉</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>burn|attack</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>OnUse,Burn,EnemyExecution,5,50,W8-023-burn,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,4,30,W8-023-attack,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>W8-024</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>爆燃阵</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>95</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>burn|core|haste</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OnUse,Burn,EnemyExecution,8,60,W8-024-burn,None,0,0,0,0,false,true|OnUse,Haste,AllAdjacentItems,1000,30,W8-024-haste,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>W8-025</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>寒镜</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>50</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>OnUse,Freeze,ShortestCooldownEnemyItem,8,8,W8-025-freeze,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>W8-026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>霜锁</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>75</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>freeze|attack</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>OnUse,Freeze,LongestCooldownEnemyItem,12,12,W8-026-freeze,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,4,30,W8-026-attack,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W8-027</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>冰封塔</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>110</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>freeze|core|slow</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>OnUse,Freeze,ShortestCooldownEnemyItem,16,16,W8-027-freeze,None,0,0,0,0,false,true|OnUse,Delay,ShortestCooldownEnemyItem,1000,40,W8-027-slow,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>W8-028</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>过载电池</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>36</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>overload</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>overload|charge</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>OnUse,Charge,Self,2,30,W8-028-charge,None,0,0,0,0,false,true|OnUse,Noise,Self,2,30,W8-028-overload,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>W8-029</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>泄压阀</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>55</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>overload</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>overload|shield</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>OnUse,Noise,Self,-4,30,W8-029-vent,None,0,0,0,0,false,true|OnUse,Buffer,Self,4,30,W8-029-shield,None,0,0,0,0,false,true</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>W8-030</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>稳压核心</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>80</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>overload</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>overload|core|charge|shield</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>OnUse,Buffer,Self,9,30,W8-030-shield,None,0,0,0,0,false,true|OnUse,Charge,RightAdjacentItem,2,30,W8-030-pass-charge,None,0,0,0,0,false,true|OnUse,Noise,Self,-3,30,W8-030-vent,None,0,0,0,0,false,true</t>
         </is>
       </c>
     </row>

--- a/Design/Excel/GameHot/Datas/Buqi/BuqiItem.xlsx
+++ b/Design/Excel/GameHot/Datas/Buqi/BuqiItem.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiItem" sheetId="1" r:id="R3a8b6e69a5404a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiItem" sheetId="1" r:id="Rbcbc3dee2d964224"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -571,9 +571,9 @@
       <x:c r="P4" t="str">
         <x:v>OnUse,Damage,EnemyExecution,4,30,W8-003-attack,None,0,0,0,0,false,true|OnUse,Haste,LeftAdjacentItem,2000,30,W8-003-haste,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q4" t="str"/>
+      <x:c r="Q4"/>
       <x:c r="R4" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S4" t="str">
         <x:v>Buqi.Content.Item.W8_003.Upgrade</x:v>
@@ -629,9 +629,9 @@
       <x:c r="P5" t="str">
         <x:v>OnAdjacentUse,Charge,Self,1,30,W8-005-adjacent-charge,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,6,30,W8-005-attack,None,0,0,3,2,true,true</x:v>
       </x:c>
-      <x:c r="Q5" t="str"/>
+      <x:c r="Q5"/>
       <x:c r="R5" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S5" t="str">
         <x:v>Buqi.Content.Item.W8_005.Upgrade</x:v>
@@ -687,9 +687,9 @@
       <x:c r="P6" t="str">
         <x:v>OnBattleStart,Haste,AllAdjacentItems,1500,50,W8-006-opening-haste,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,16,30,W8-006-attack,None,0,0,0,0,false,true|OnUse,Noise,Self,2,30,W8-006-overload,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q6" t="str"/>
+      <x:c r="Q6"/>
       <x:c r="R6" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S6" t="str">
         <x:v>Buqi.Content.Item.W8_006.Upgrade</x:v>
@@ -745,9 +745,9 @@
       <x:c r="P7" t="str">
         <x:v>OnUse,Buffer,Self,7,30,W8-007-shield,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q7" t="str"/>
+      <x:c r="Q7"/>
       <x:c r="R7" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S7" t="str">
         <x:v>Buqi.Content.Item.W8_007.Upgrade</x:v>
@@ -803,9 +803,9 @@
       <x:c r="P8" t="str">
         <x:v>OnUse,Charge,Self,1,30,W8-008-charge,None,0,0,0,0,false,true|OnFirstConditionMet,Damage,EnemyExecution,8,30,W8-008-shield-break,BufferLost,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q8" t="str"/>
+      <x:c r="Q8"/>
       <x:c r="R8" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S8" t="str">
         <x:v>Buqi.Content.Item.W8_008.Upgrade</x:v>
@@ -861,9 +861,9 @@
       <x:c r="P9" t="str">
         <x:v>OnUse,Buffer,Self,12,30,W8-012-shield,None,0,0,0,0,false,true|OnFirstConditionMet,Damage,EnemyExecution,14,30,W8-012-shield-break,BufferLost,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q9" t="str"/>
+      <x:c r="Q9"/>
       <x:c r="R9" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S9" t="str">
         <x:v>Buqi.Content.Item.W8_012.Upgrade</x:v>
@@ -919,9 +919,9 @@
       <x:c r="P10" t="str">
         <x:v>OnUse,Damage,EnemyExecution,4,30,W8-013-attack,None,0,0,0,0,false,true|OnUse,Charge,RightAdjacentItem,1,30,W8-013-pass-charge,None,0,0,0,0,false,true|OnAdjacentUse,Charge,RightAdjacentItem,1,30,W8-013-adjacent-pass,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q10" t="str"/>
+      <x:c r="Q10"/>
       <x:c r="R10" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S10" t="str">
         <x:v>Buqi.Content.Item.W8_013.Upgrade</x:v>
@@ -977,9 +977,9 @@
       <x:c r="P11" t="str">
         <x:v>OnAdjacentUse,Charge,Self,1,30,W8-014-adjacent-charge,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,3,30,W8-014-attack,None,0,0,2,3,true,true</x:v>
       </x:c>
-      <x:c r="Q11" t="str"/>
+      <x:c r="Q11"/>
       <x:c r="R11" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S11" t="str">
         <x:v>Buqi.Content.Item.W8_014.Upgrade</x:v>
@@ -1035,9 +1035,9 @@
       <x:c r="P12" t="str">
         <x:v>OnAdjacentUse,Haste,Self,2000,30,W8-015-adjacent-haste,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,7,30,W8-015-attack,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q12" t="str"/>
+      <x:c r="Q12"/>
       <x:c r="R12" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S12" t="str">
         <x:v>Buqi.Content.Item.W8_015.Upgrade</x:v>
@@ -1093,9 +1093,9 @@
       <x:c r="P13" t="str">
         <x:v>OnUse,Heal,Self,8,30,W8-016-heal,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q13" t="str"/>
+      <x:c r="Q13"/>
       <x:c r="R13" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S13" t="str">
         <x:v>Buqi.Content.Item.W8_016.Upgrade</x:v>
@@ -1151,9 +1151,9 @@
       <x:c r="P14" t="str">
         <x:v>OnUse,Regen,Self,4,50,W8-017-regen,None,0,0,0,0,false,true|OnUse,Buffer,Self,5,30,W8-017-shield,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q14" t="str"/>
+      <x:c r="Q14"/>
       <x:c r="R14" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S14" t="str">
         <x:v>Buqi.Content.Item.W8_017.Upgrade</x:v>
@@ -1209,9 +1209,9 @@
       <x:c r="P15" t="str">
         <x:v>OnBattleStart,Regen,Self,3,60,W8-018-opening-regen,None,0,0,0,0,false,true|OnUse,Heal,Self,15,30,W8-018-heal,None,0,0,0,0,false,true|OnUse,Haste,AllAdjacentItems,1200,30,W8-018-haste,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q15" t="str"/>
+      <x:c r="Q15"/>
       <x:c r="R15" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S15" t="str">
         <x:v>Buqi.Content.Item.W8_018.Upgrade</x:v>
@@ -1267,9 +1267,9 @@
       <x:c r="P16" t="str">
         <x:v>OnUse,Poison,EnemyExecution,3,40,W8-019-poison,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q16" t="str"/>
+      <x:c r="Q16"/>
       <x:c r="R16" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S16" t="str">
         <x:v>Buqi.Content.Item.W8_019.Upgrade</x:v>
@@ -1325,9 +1325,9 @@
       <x:c r="P17" t="str">
         <x:v>OnUse,Poison,EnemyExecution,5,50,W8-020-poison,None,0,0,0,0,false,true|OnUse,Delay,ShortestCooldownEnemyItem,1000,30,W8-020-slow,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q17" t="str"/>
+      <x:c r="Q17"/>
       <x:c r="R17" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S17" t="str">
         <x:v>Buqi.Content.Item.W8_020.Upgrade</x:v>
@@ -1383,9 +1383,9 @@
       <x:c r="P18" t="str">
         <x:v>OnUse,Poison,EnemyExecution,7,60,W8-021-poison,None,0,0,0,0,false,true|OnUse,Noise,Self,1,30,W8-021-overload,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q18" t="str"/>
+      <x:c r="Q18"/>
       <x:c r="R18" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S18" t="str">
         <x:v>Buqi.Content.Item.W8_021.Upgrade</x:v>
@@ -1441,9 +1441,9 @@
       <x:c r="P19" t="str">
         <x:v>OnUse,Burn,EnemyExecution,3,30,W8-022-burn,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q19" t="str"/>
+      <x:c r="Q19"/>
       <x:c r="R19" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S19" t="str">
         <x:v>Buqi.Content.Item.W8_022.Upgrade</x:v>
@@ -1499,9 +1499,9 @@
       <x:c r="P20" t="str">
         <x:v>OnUse,Burn,EnemyExecution,5,50,W8-023-burn,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,4,30,W8-023-attack,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q20" t="str"/>
+      <x:c r="Q20"/>
       <x:c r="R20" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S20" t="str">
         <x:v>Buqi.Content.Item.W8_023.Upgrade</x:v>
@@ -1557,9 +1557,9 @@
       <x:c r="P21" t="str">
         <x:v>OnUse,Burn,EnemyExecution,8,60,W8-024-burn,None,0,0,0,0,false,true|OnUse,Haste,AllAdjacentItems,1000,30,W8-024-haste,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q21" t="str"/>
+      <x:c r="Q21"/>
       <x:c r="R21" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S21" t="str">
         <x:v>Buqi.Content.Item.W8_024.Upgrade</x:v>
@@ -1615,9 +1615,9 @@
       <x:c r="P22" t="str">
         <x:v>OnUse,Freeze,ShortestCooldownEnemyItem,8,8,W8-025-freeze,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q22" t="str"/>
+      <x:c r="Q22"/>
       <x:c r="R22" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S22" t="str">
         <x:v>Buqi.Content.Item.W8_025.Upgrade</x:v>
@@ -1673,9 +1673,9 @@
       <x:c r="P23" t="str">
         <x:v>OnUse,Freeze,LongestCooldownEnemyItem,12,12,W8-026-freeze,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,4,30,W8-026-attack,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q23" t="str"/>
+      <x:c r="Q23"/>
       <x:c r="R23" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S23" t="str">
         <x:v>Buqi.Content.Item.W8_026.Upgrade</x:v>
@@ -1731,9 +1731,9 @@
       <x:c r="P24" t="str">
         <x:v>OnUse,Freeze,ShortestCooldownEnemyItem,16,16,W8-027-freeze,None,0,0,0,0,false,true|OnUse,Delay,ShortestCooldownEnemyItem,1000,40,W8-027-slow,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q24" t="str"/>
+      <x:c r="Q24"/>
       <x:c r="R24" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S24" t="str">
         <x:v>Buqi.Content.Item.W8_027.Upgrade</x:v>
@@ -1789,9 +1789,9 @@
       <x:c r="P25" t="str">
         <x:v>OnUse,Charge,Self,2,30,W8-028-charge,None,0,0,0,0,false,true|OnUse,Noise,Self,2,30,W8-028-overload,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q25" t="str"/>
+      <x:c r="Q25"/>
       <x:c r="R25" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S25" t="str">
         <x:v>Buqi.Content.Item.W8_028.Upgrade</x:v>
@@ -1847,9 +1847,9 @@
       <x:c r="P26" t="str">
         <x:v>OnUse,Noise,Self,-4,30,W8-029-vent,None,0,0,0,0,false,true|OnUse,Buffer,Self,4,30,W8-029-shield,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q26" t="str"/>
+      <x:c r="Q26"/>
       <x:c r="R26" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S26" t="str">
         <x:v>Buqi.Content.Item.W8_029.Upgrade</x:v>
@@ -1905,9 +1905,9 @@
       <x:c r="P27" t="str">
         <x:v>OnUse,Buffer,Self,9,30,W8-030-shield,None,0,0,0,0,false,true|OnUse,Charge,RightAdjacentItem,2,30,W8-030-pass-charge,None,0,0,0,0,false,true|OnUse,Noise,Self,-3,30,W8-030-vent,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q27" t="str"/>
+      <x:c r="Q27"/>
       <x:c r="R27" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S27" t="str">
         <x:v>Buqi.Content.Item.W8_030.Upgrade</x:v>
@@ -1963,9 +1963,9 @@
       <x:c r="P28" t="str">
         <x:v>OnUse,Haste,AllAdjacentItems,800,30,W8-031-adjacent-haste,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q28" t="str"/>
+      <x:c r="Q28"/>
       <x:c r="R28" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S28" t="str">
         <x:v>Buqi.Content.Item.W8_031.Upgrade</x:v>
@@ -2021,9 +2021,9 @@
       <x:c r="P29" t="str">
         <x:v>OnUse,Damage,EnemyExecution,3,30,W8-032-attack,None,0,0,0,0,false,true|OnAdjacentUse,Charge,RightAdjacentItem,1,30,W8-032-pass-charge,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q29" t="str"/>
+      <x:c r="Q29"/>
       <x:c r="R29" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S29" t="str">
         <x:v>Buqi.Content.Item.W8_032.Upgrade</x:v>
@@ -2079,9 +2079,9 @@
       <x:c r="P30" t="str">
         <x:v>OnUse,Damage,EnemyExecution,4,30,W8-033-attack,None,0,0,0,0,false,true|OnUse,Buffer,Self,5,30,W8-033-buffer,None,0,0,0,0,false,true|OnFirstInterfered,Haste,AllAdjacentItems,1000,30,W8-033-recover-haste,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q30" t="str"/>
+      <x:c r="Q30"/>
       <x:c r="R30" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S30" t="str">
         <x:v>Buqi.Content.Item.W8_033.Upgrade</x:v>
@@ -2137,9 +2137,9 @@
       <x:c r="P31" t="str">
         <x:v>OnUse,Damage,EnemyExecution,4,30,W8-034-attack,None,0,0,0,0,false,true|OnUse,Burn,EnemyExecution,3,30,W8-034-burn,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q31" t="str"/>
+      <x:c r="Q31"/>
       <x:c r="R31" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S31" t="str">
         <x:v>Buqi.Content.Item.W8_034.Upgrade</x:v>
@@ -2199,7 +2199,7 @@
         <x:v>OnBattleEndDamage,GainCoin,1,12,1,W8-035-damage-dividend</x:v>
       </x:c>
       <x:c r="R32" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S32" t="str">
         <x:v>Buqi.Content.Item.W8_035.Upgrade</x:v>
@@ -2255,9 +2255,9 @@
       <x:c r="P33" t="str">
         <x:v>OnUse,Buffer,Self,4,30,W8-036-buffer,None,0,0,0,0,false,true|OnAdjacentUse,Buffer,Self,3,30,W8-036-adjacent-buffer,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q33" t="str"/>
+      <x:c r="Q33"/>
       <x:c r="R33" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S33" t="str">
         <x:v>Buqi.Content.Item.W8_036.Upgrade</x:v>
@@ -2313,9 +2313,9 @@
       <x:c r="P34" t="str">
         <x:v>OnUse,Buffer,Self,4,30,W8-037-buffer,None,0,0,0,0,false,true|OnUse,Charge,RightAdjacentItem,1,30,W8-037-pass-charge,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q34" t="str"/>
+      <x:c r="Q34"/>
       <x:c r="R34" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S34" t="str">
         <x:v>Buqi.Content.Item.W8_037.Upgrade</x:v>
@@ -2371,9 +2371,9 @@
       <x:c r="P35" t="str">
         <x:v>OnUse,Buffer,Self,6,30,W8-038-buffer,None,0,0,0,0,false,true|OnUse,Regen,Self,2,30,W8-038-regen,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q35" t="str"/>
+      <x:c r="Q35"/>
       <x:c r="R35" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S35" t="str">
         <x:v>Buqi.Content.Item.W8_038.Upgrade</x:v>
@@ -2429,9 +2429,9 @@
       <x:c r="P36" t="str">
         <x:v>OnUse,Heal,Self,8,30,W8-039-heal,None,0,0,0,0,false,true|OnUse,Buffer,Self,4,30,W8-039-buffer,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q36" t="str"/>
+      <x:c r="Q36"/>
       <x:c r="R36" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S36" t="str">
         <x:v>Buqi.Content.Item.W8_039.Upgrade</x:v>
@@ -2491,7 +2491,7 @@
         <x:v>OnBattleEndBufferAbsorbed,GainCoin,1,12,1,W8-040-buffer-dividend</x:v>
       </x:c>
       <x:c r="R37" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S37" t="str">
         <x:v>Buqi.Content.Item.W8_040.Upgrade</x:v>
@@ -2547,9 +2547,9 @@
       <x:c r="P38" t="str">
         <x:v>OnUse,Regen,Self,2,30,W8-041-regen,None,0,0,0,0,false,true|OnAdjacentUse,Heal,Self,2,30,W8-041-adjacent-heal,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q38" t="str"/>
+      <x:c r="Q38"/>
       <x:c r="R38" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S38" t="str">
         <x:v>Buqi.Content.Item.W8_041.Upgrade</x:v>
@@ -2605,9 +2605,9 @@
       <x:c r="P39" t="str">
         <x:v>OnUse,Heal,Self,4,30,W8-042-heal,None,0,0,0,0,false,true|OnUse,Haste,RightAdjacentItem,800,30,W8-042-pass-haste,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q39" t="str"/>
+      <x:c r="Q39"/>
       <x:c r="R39" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S39" t="str">
         <x:v>Buqi.Content.Item.W8_042.Upgrade</x:v>
@@ -2663,9 +2663,9 @@
       <x:c r="P40" t="str">
         <x:v>OnUse,Heal,Self,6,30,W8-043-heal,None,0,0,0,0,false,true|OnUse,Damage,EnemyExecution,5,30,W8-043-attack,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q40" t="str"/>
+      <x:c r="Q40"/>
       <x:c r="R40" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S40" t="str">
         <x:v>Buqi.Content.Item.W8_043.Upgrade</x:v>
@@ -2721,9 +2721,9 @@
       <x:c r="P41" t="str">
         <x:v>OnBattleStart,Buffer,Self,10,30,W8-044-opening-buffer,None,0,0,0,0,false,true|OnBattleStart,Regen,Self,3,30,W8-044-opening-regen,None,0,0,0,0,false,true|OnUse,Heal,Self,5,30,W8-044-heal,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q41" t="str"/>
+      <x:c r="Q41"/>
       <x:c r="R41" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S41" t="str">
         <x:v>Buqi.Content.Item.W8_044.Upgrade</x:v>
@@ -2783,7 +2783,7 @@
         <x:v>OnBattleEndHealing,GainCoin,1,10,1,W8-045-heal-dividend</x:v>
       </x:c>
       <x:c r="R42" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S42" t="str">
         <x:v>Buqi.Content.Item.W8_045.Upgrade</x:v>
@@ -2839,9 +2839,9 @@
       <x:c r="P43" t="str">
         <x:v>OnUse,Haste,AllAdjacentItems,800,30,W8-046-adjacent-haste,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q43" t="str"/>
+      <x:c r="Q43"/>
       <x:c r="R43" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S43" t="str">
         <x:v>Buqi.Content.Item.W8_046.Upgrade</x:v>
@@ -2901,7 +2901,7 @@
         <x:v>OnFirstPurchaseOrUpgrade,DiscountCoin,1,0,1,W8-047-first-discount</x:v>
       </x:c>
       <x:c r="R44" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S44" t="str">
         <x:v>Buqi.Content.Item.W8_047.Upgrade</x:v>
@@ -2957,9 +2957,9 @@
       <x:c r="P45" t="str">
         <x:v>OnUse,Heal,Self,4,30,W8-048-heal,None,0,0,0,0,false,true|OnFirstInterfered,Buffer,Self,8,30,W8-048-counter-buffer,None,0,0,0,0,false,true|OnFirstInterfered,Haste,AllAdjacentItems,1000,30,W8-048-counter-haste,None,0,0,0,0,false,true</x:v>
       </x:c>
-      <x:c r="Q45" t="str"/>
+      <x:c r="Q45"/>
       <x:c r="R45" t="str">
-        <x:v>改良：效果数值按 1.6 倍结算；定型：效果数值按 2.4 倍结算；冷却不变。</x:v>
+        <x:v>强化：效果数值按 1.6 倍结算；高级：效果数值按 2.4 倍结算；冷却不变。</x:v>
       </x:c>
       <x:c r="S45" t="str">
         <x:v>Buqi.Content.Item.W8_048.Upgrade</x:v>
